--- a/교재/엑셀교재v2/025_데이터표_실습.xlsx
+++ b/교재/엑셀교재v2/025_데이터표_실습.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3B1EAE-7184-48C8-9083-4551C90D9196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04044B6A-5D0F-4FDC-A3B6-0AE7EAFA76E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24075" yWindow="810" windowWidth="22200" windowHeight="14790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>025 데이터 표 사용 안내</t>
   </si>
@@ -294,14 +294,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -528,7 +528,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14"/>
@@ -908,10 +908,10 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="15"/>
+      <c r="C1" s="13"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="14" t="s">
@@ -945,12 +945,12 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1">
       <c r="A4" s="1"/>
@@ -1218,9 +1218,7 @@
     </row>
     <row r="22" spans="1:10" ht="30" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -1302,10 +1300,10 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="15"/>
+      <c r="C1" s="13"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="14" t="s">
@@ -1339,12 +1337,12 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1">
       <c r="A4" s="1"/>
@@ -1769,10 +1767,10 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
@@ -2149,10 +2147,10 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
